--- a/data/nb_rates.xlsx
+++ b/data/nb_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,7 +711,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 Венгерских форинтов </t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAR </t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1413,7 +1413,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 Венгерских форинтов </t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAR </t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2115,7 +2115,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 Венгерских форинтов </t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2313,16 +2313,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>NZD via Yahoo annual NZDUSD=X × NBK annual USD/KZT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NZD</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>108.75</v>
+        <v>280.3526842089996</v>
       </c>
       <c r="D106" t="n">
         <v>2023</v>
@@ -2331,16 +2331,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5.4</v>
+        <v>108.75</v>
       </c>
       <c r="D107" t="n">
         <v>2023</v>
@@ -2349,16 +2349,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>121.63</v>
+        <v>5.4</v>
       </c>
       <c r="D108" t="n">
         <v>2023</v>
@@ -2367,16 +2367,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>43</v>
+        <v>121.63</v>
       </c>
       <c r="D109" t="n">
         <v>2023</v>
@@ -2385,16 +2385,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>339.78</v>
+        <v>43</v>
       </c>
       <c r="D110" t="n">
         <v>2023</v>
@@ -2403,16 +2403,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13.12</v>
+        <v>339.78</v>
       </c>
       <c r="D111" t="n">
         <v>2023</v>
@@ -2421,16 +2421,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>42.16</v>
+        <v>13.12</v>
       </c>
       <c r="D112" t="n">
         <v>2023</v>
@@ -2439,16 +2439,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>19.73</v>
+        <v>42.16</v>
       </c>
       <c r="D113" t="n">
         <v>2023</v>
@@ -2457,16 +2457,16 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12.42</v>
+        <v>19.73</v>
       </c>
       <c r="D114" t="n">
         <v>2023</v>
@@ -2475,16 +2475,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>456.31</v>
+        <v>12.42</v>
       </c>
       <c r="D115" t="n">
         <v>2023</v>
@@ -2493,16 +2493,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3.9</v>
+        <v>456.31</v>
       </c>
       <c r="D116" t="n">
         <v>2023</v>
@@ -2511,16 +2511,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>608.53</v>
+        <v>3.9</v>
       </c>
       <c r="D117" t="n">
         <v>2023</v>
@@ -2529,16 +2529,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAR </t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>24.75</v>
+        <v>608.53</v>
       </c>
       <c r="D118" t="n">
         <v>2023</v>
@@ -2547,34 +2547,34 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Дирхам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>125.38</v>
+        <v>24.75</v>
       </c>
       <c r="D119" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дирхам ОАЭ</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10.75</v>
+        <v>125.38</v>
       </c>
       <c r="D120" t="n">
         <v>2022</v>
@@ -2583,16 +2583,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>319.6</v>
+        <v>10.75</v>
       </c>
       <c r="D121" t="n">
         <v>2022</v>
@@ -2601,16 +2601,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>271.92</v>
+        <v>319.6</v>
       </c>
       <c r="D122" t="n">
         <v>2022</v>
@@ -2619,16 +2619,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>89.38</v>
+        <v>271.92</v>
       </c>
       <c r="D123" t="n">
         <v>2022</v>
@@ -2637,16 +2637,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>167.76</v>
+        <v>89.38</v>
       </c>
       <c r="D124" t="n">
         <v>2022</v>
@@ -2655,16 +2655,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>353.92</v>
+        <v>167.76</v>
       </c>
       <c r="D125" t="n">
         <v>2022</v>
@@ -2673,16 +2673,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>482.6</v>
+        <v>353.92</v>
       </c>
       <c r="D126" t="n">
         <v>2022</v>
@@ -2691,16 +2691,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>68.45999999999999</v>
+        <v>482.6</v>
       </c>
       <c r="D127" t="n">
         <v>2022</v>
@@ -2709,16 +2709,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>19.73</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="D128" t="n">
         <v>2022</v>
@@ -2727,16 +2727,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>65.09999999999999</v>
+        <v>19.73</v>
       </c>
       <c r="D129" t="n">
         <v>2022</v>
@@ -2745,16 +2745,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>484.22</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D130" t="n">
         <v>2022</v>
@@ -2763,35 +2763,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>484.22</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C131" t="n">
+      <c r="C132" t="n">
         <v>568.22</v>
-      </c>
-      <c r="D131" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>160.79</v>
       </c>
       <c r="D132" t="n">
         <v>2022</v>
@@ -2800,16 +2800,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>58.8</v>
+        <v>160.79</v>
       </c>
       <c r="D133" t="n">
         <v>2022</v>
@@ -2818,16 +2818,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>12.42</v>
+        <v>58.8</v>
       </c>
       <c r="D134" t="n">
         <v>2022</v>
@@ -2836,16 +2836,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5.86</v>
+        <v>12.42</v>
       </c>
       <c r="D135" t="n">
         <v>2022</v>
@@ -2854,16 +2854,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10.96</v>
+        <v>5.86</v>
       </c>
       <c r="D136" t="n">
         <v>2022</v>
@@ -2872,16 +2872,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3.52</v>
+        <v>10.96</v>
       </c>
       <c r="D137" t="n">
         <v>2022</v>
@@ -2890,16 +2890,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5.52</v>
+        <v>3.52</v>
       </c>
       <c r="D138" t="n">
         <v>2022</v>
@@ -2908,16 +2908,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>35.68</v>
+        <v>5.52</v>
       </c>
       <c r="D139" t="n">
         <v>2022</v>
@@ -2926,16 +2926,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1503.81</v>
+        <v>35.68</v>
       </c>
       <c r="D140" t="n">
         <v>2022</v>
@@ -2944,16 +2944,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>24.45</v>
+        <v>1503.81</v>
       </c>
       <c r="D141" t="n">
         <v>2022</v>
@@ -2962,16 +2962,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>22.92</v>
+        <v>24.45</v>
       </c>
       <c r="D142" t="n">
         <v>2022</v>
@@ -2980,16 +2980,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>104.7</v>
+        <v>22.92</v>
       </c>
       <c r="D143" t="n">
         <v>2022</v>
@@ -2998,16 +2998,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>47.99</v>
+        <v>104.7</v>
       </c>
       <c r="D144" t="n">
         <v>2022</v>
@@ -3016,16 +3016,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>103.42</v>
+        <v>47.99</v>
       </c>
       <c r="D145" t="n">
         <v>2022</v>
@@ -3034,16 +3034,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6.96</v>
+        <v>103.42</v>
       </c>
       <c r="D146" t="n">
         <v>2022</v>
@@ -3052,16 +3052,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>122.64</v>
+        <v>6.96</v>
       </c>
       <c r="D147" t="n">
         <v>2022</v>
@@ -3070,16 +3070,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>45.6</v>
+        <v>122.64</v>
       </c>
       <c r="D148" t="n">
         <v>2022</v>
@@ -3088,16 +3088,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>334</v>
+        <v>45.6</v>
       </c>
       <c r="D149" t="n">
         <v>2022</v>
@@ -3106,16 +3106,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>13.15</v>
+        <v>334</v>
       </c>
       <c r="D150" t="n">
         <v>2022</v>
@@ -3124,16 +3124,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>42.7</v>
+        <v>13.15</v>
       </c>
       <c r="D151" t="n">
         <v>2022</v>
@@ -3142,16 +3142,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>28.01</v>
+        <v>42.7</v>
       </c>
       <c r="D152" t="n">
         <v>2022</v>
@@ -3160,16 +3160,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>14.26</v>
+        <v>28.01</v>
       </c>
       <c r="D153" t="n">
         <v>2022</v>
@@ -3178,16 +3178,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>460.48</v>
+        <v>14.26</v>
       </c>
       <c r="D154" t="n">
         <v>2022</v>
@@ -3196,16 +3196,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4.18</v>
+        <v>460.48</v>
       </c>
       <c r="D155" t="n">
         <v>2022</v>
@@ -3214,16 +3214,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>615.63</v>
+        <v>4.18</v>
       </c>
       <c r="D156" t="n">
         <v>2022</v>
@@ -3232,16 +3232,16 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>28.2</v>
+        <v>615.63</v>
       </c>
       <c r="D157" t="n">
         <v>2022</v>
@@ -3250,34 +3250,34 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Дирхам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>116</v>
+        <v>28.2</v>
       </c>
       <c r="D158" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дирхам ОАЭ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8.49</v>
+        <v>116</v>
       </c>
       <c r="D159" t="n">
         <v>2021</v>
@@ -3286,16 +3286,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>319.95</v>
+        <v>8.49</v>
       </c>
       <c r="D160" t="n">
         <v>2021</v>
@@ -3304,16 +3304,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>251.64</v>
+        <v>319.95</v>
       </c>
       <c r="D161" t="n">
         <v>2021</v>
@@ -3322,16 +3322,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>79.11</v>
+        <v>251.64</v>
       </c>
       <c r="D162" t="n">
         <v>2021</v>
@@ -3340,16 +3340,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>168.26</v>
+        <v>79.11</v>
       </c>
       <c r="D163" t="n">
         <v>2021</v>
@@ -3358,16 +3358,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>340.01</v>
+        <v>168.26</v>
       </c>
       <c r="D164" t="n">
         <v>2021</v>
@@ -3376,16 +3376,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>466.13</v>
+        <v>340.01</v>
       </c>
       <c r="D165" t="n">
         <v>2021</v>
@@ -3394,16 +3394,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>66.06999999999999</v>
+        <v>466.13</v>
       </c>
       <c r="D166" t="n">
         <v>2021</v>
@@ -3412,16 +3412,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>19.66</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="D167" t="n">
         <v>2021</v>
@@ -3430,16 +3430,16 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>67.77</v>
+        <v>19.66</v>
       </c>
       <c r="D168" t="n">
         <v>2021</v>
@@ -3448,16 +3448,16 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>503.88</v>
+        <v>67.77</v>
       </c>
       <c r="D169" t="n">
         <v>2021</v>
@@ -3466,35 +3466,35 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>503.88</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C170" t="n">
+      <c r="C171" t="n">
         <v>586.25</v>
-      </c>
-      <c r="D170" t="n">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>133.46</v>
       </c>
       <c r="D171" t="n">
         <v>2021</v>
@@ -3503,16 +3503,16 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>54.81</v>
+        <v>133.46</v>
       </c>
       <c r="D172" t="n">
         <v>2021</v>
@@ -3521,16 +3521,16 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>14.08</v>
+        <v>54.81</v>
       </c>
       <c r="D173" t="n">
         <v>2021</v>
@@ -3539,16 +3539,16 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5.76</v>
+        <v>14.08</v>
       </c>
       <c r="D174" t="n">
         <v>2021</v>
@@ -3557,16 +3557,16 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>10.14</v>
+        <v>5.76</v>
       </c>
       <c r="D175" t="n">
         <v>2021</v>
@@ -3575,16 +3575,16 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3.88</v>
+        <v>10.14</v>
       </c>
       <c r="D176" t="n">
         <v>2021</v>
@@ -3593,16 +3593,16 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5.03</v>
+        <v>3.88</v>
       </c>
       <c r="D177" t="n">
         <v>2021</v>
@@ -3611,16 +3611,16 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>37.23</v>
+        <v>5.03</v>
       </c>
       <c r="D178" t="n">
         <v>2021</v>
@@ -3629,16 +3629,16 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1413.59</v>
+        <v>37.23</v>
       </c>
       <c r="D179" t="n">
         <v>2021</v>
@@ -3647,16 +3647,16 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>24.22</v>
+        <v>1413.59</v>
       </c>
       <c r="D180" t="n">
         <v>2021</v>
@@ -3665,16 +3665,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>21.02</v>
+        <v>24.22</v>
       </c>
       <c r="D181" t="n">
         <v>2021</v>
@@ -3683,16 +3683,16 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>102.84</v>
+        <v>21.02</v>
       </c>
       <c r="D182" t="n">
         <v>2021</v>
@@ -3701,16 +3701,16 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>49.61</v>
+        <v>102.84</v>
       </c>
       <c r="D183" t="n">
         <v>2021</v>
@@ -3719,16 +3719,16 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>110.45</v>
+        <v>49.61</v>
       </c>
       <c r="D184" t="n">
         <v>2021</v>
@@ -3737,16 +3737,16 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>5.79</v>
+        <v>110.45</v>
       </c>
       <c r="D185" t="n">
         <v>2021</v>
@@ -3755,16 +3755,16 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>113.59</v>
+        <v>5.79</v>
       </c>
       <c r="D186" t="n">
         <v>2021</v>
@@ -3773,16 +3773,16 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>49.69</v>
+        <v>113.59</v>
       </c>
       <c r="D187" t="n">
         <v>2021</v>
@@ -3791,16 +3791,16 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>317.1</v>
+        <v>49.69</v>
       </c>
       <c r="D188" t="n">
         <v>2021</v>
@@ -3809,16 +3809,16 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>13.33</v>
+        <v>317.1</v>
       </c>
       <c r="D189" t="n">
         <v>2021</v>
@@ -3827,16 +3827,16 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>37.7</v>
+        <v>13.33</v>
       </c>
       <c r="D190" t="n">
         <v>2021</v>
@@ -3845,16 +3845,16 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>49.42</v>
+        <v>37.7</v>
       </c>
       <c r="D191" t="n">
         <v>2021</v>
@@ -3863,16 +3863,16 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>15.65</v>
+        <v>49.42</v>
       </c>
       <c r="D192" t="n">
         <v>2021</v>
@@ -3881,16 +3881,16 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>426.03</v>
+        <v>15.65</v>
       </c>
       <c r="D193" t="n">
         <v>2021</v>
@@ -3899,16 +3899,16 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>4.02</v>
+        <v>426.03</v>
       </c>
       <c r="D194" t="n">
         <v>2021</v>
@@ -3917,16 +3917,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>606.87</v>
+        <v>4.02</v>
       </c>
       <c r="D195" t="n">
         <v>2021</v>
@@ -3935,16 +3935,16 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>28.89</v>
+        <v>606.87</v>
       </c>
       <c r="D196" t="n">
         <v>2021</v>
@@ -3953,34 +3953,34 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>112.44</v>
+        <v>28.89</v>
       </c>
       <c r="D197" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8.48</v>
+        <v>112.44</v>
       </c>
       <c r="D198" t="n">
         <v>2020</v>
@@ -3989,16 +3989,16 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>285.13</v>
+        <v>8.48</v>
       </c>
       <c r="D199" t="n">
         <v>2020</v>
@@ -4007,16 +4007,16 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>243.93</v>
+        <v>285.13</v>
       </c>
       <c r="D200" t="n">
         <v>2020</v>
@@ -4025,16 +4025,16 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>80.69</v>
+        <v>243.93</v>
       </c>
       <c r="D201" t="n">
         <v>2020</v>
@@ -4043,16 +4043,16 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>169.94</v>
+        <v>80.69</v>
       </c>
       <c r="D202" t="n">
         <v>2020</v>
@@ -4061,16 +4061,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>308.17</v>
+        <v>169.94</v>
       </c>
       <c r="D203" t="n">
         <v>2020</v>
@@ -4079,16 +4079,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>440.52</v>
+        <v>308.17</v>
       </c>
       <c r="D204" t="n">
         <v>2020</v>
@@ -4097,16 +4097,16 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>59.89</v>
+        <v>440.52</v>
       </c>
       <c r="D205" t="n">
         <v>2020</v>
@@ -4115,16 +4115,16 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>17.83</v>
+        <v>59.89</v>
       </c>
       <c r="D206" t="n">
         <v>2020</v>
@@ -4133,16 +4133,16 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>63.26</v>
+        <v>17.83</v>
       </c>
       <c r="D207" t="n">
         <v>2020</v>
@@ -4151,16 +4151,16 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>471.44</v>
+        <v>63.26</v>
       </c>
       <c r="D208" t="n">
         <v>2020</v>
@@ -4169,35 +4169,35 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>471.44</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C209" t="n">
+      <c r="C210" t="n">
         <v>529.91</v>
-      </c>
-      <c r="D209" t="n">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>133.97</v>
       </c>
       <c r="D210" t="n">
         <v>2020</v>
@@ -4206,16 +4206,16 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>53.24</v>
+        <v>133.97</v>
       </c>
       <c r="D211" t="n">
         <v>2020</v>
@@ -4224,16 +4224,16 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>13.42</v>
+        <v>53.24</v>
       </c>
       <c r="D212" t="n">
         <v>2020</v>
@@ -4242,16 +4242,16 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>5.57</v>
+        <v>13.42</v>
       </c>
       <c r="D213" t="n">
         <v>2020</v>
@@ -4260,16 +4260,16 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9.84</v>
+        <v>5.57</v>
       </c>
       <c r="D214" t="n">
         <v>2020</v>
@@ -4278,16 +4278,16 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3.87</v>
+        <v>9.84</v>
       </c>
       <c r="D215" t="n">
         <v>2020</v>
@@ -4296,16 +4296,16 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>5.36</v>
+        <v>3.87</v>
       </c>
       <c r="D216" t="n">
         <v>2020</v>
@@ -4314,16 +4314,16 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>35.06</v>
+        <v>5.36</v>
       </c>
       <c r="D217" t="n">
         <v>2020</v>
@@ -4332,16 +4332,16 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1347.18</v>
+        <v>35.06</v>
       </c>
       <c r="D218" t="n">
         <v>2020</v>
@@ -4350,16 +4350,16 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>24.03</v>
+        <v>1347.18</v>
       </c>
       <c r="D219" t="n">
         <v>2020</v>
@@ -4368,16 +4368,16 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>19.33</v>
+        <v>24.03</v>
       </c>
       <c r="D220" t="n">
         <v>2020</v>
@@ -4386,16 +4386,16 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>98.37</v>
+        <v>19.33</v>
       </c>
       <c r="D221" t="n">
         <v>2020</v>
@@ -4404,16 +4404,16 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>44.01</v>
+        <v>98.37</v>
       </c>
       <c r="D222" t="n">
         <v>2020</v>
@@ -4422,16 +4422,16 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>106.11</v>
+        <v>44.01</v>
       </c>
       <c r="D223" t="n">
         <v>2020</v>
@@ -4440,16 +4440,16 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>5.73</v>
+        <v>106.11</v>
       </c>
       <c r="D224" t="n">
         <v>2020</v>
@@ -4458,16 +4458,16 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>110.06</v>
+        <v>5.73</v>
       </c>
       <c r="D225" t="n">
         <v>2020</v>
@@ -4476,16 +4476,16 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>45.02</v>
+        <v>110.06</v>
       </c>
       <c r="D226" t="n">
         <v>2020</v>
@@ -4494,16 +4494,16 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>299.5</v>
+        <v>45.02</v>
       </c>
       <c r="D227" t="n">
         <v>2020</v>
@@ -4512,16 +4512,16 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>13.2</v>
+        <v>299.5</v>
       </c>
       <c r="D228" t="n">
         <v>2020</v>
@@ -4530,16 +4530,16 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>40.13</v>
+        <v>13.2</v>
       </c>
       <c r="D229" t="n">
         <v>2020</v>
@@ -4548,16 +4548,16 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>59.25</v>
+        <v>40.13</v>
       </c>
       <c r="D230" t="n">
         <v>2020</v>
@@ -4566,16 +4566,16 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>15.34</v>
+        <v>59.25</v>
       </c>
       <c r="D231" t="n">
         <v>2020</v>
@@ -4584,16 +4584,16 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>412.95</v>
+        <v>15.34</v>
       </c>
       <c r="D232" t="n">
         <v>2020</v>
@@ -4602,16 +4602,16 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>4.12</v>
+        <v>412.95</v>
       </c>
       <c r="D233" t="n">
         <v>2020</v>
@@ -4620,16 +4620,16 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>575.3200000000001</v>
+        <v>4.12</v>
       </c>
       <c r="D234" t="n">
         <v>2020</v>
@@ -4638,16 +4638,16 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>25.21</v>
+        <v>575.3200000000001</v>
       </c>
       <c r="D235" t="n">
         <v>2020</v>
@@ -4656,34 +4656,34 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>104.21</v>
+        <v>25.21</v>
       </c>
       <c r="D236" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>7.99</v>
+        <v>104.21</v>
       </c>
       <c r="D237" t="n">
         <v>2019</v>
@@ -4692,16 +4692,16 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>266.08</v>
+        <v>7.99</v>
       </c>
       <c r="D238" t="n">
         <v>2019</v>
@@ -4710,16 +4710,16 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>226.09</v>
+        <v>266.08</v>
       </c>
       <c r="D239" t="n">
         <v>2019</v>
@@ -4728,16 +4728,16 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>97.23</v>
+        <v>226.09</v>
       </c>
       <c r="D240" t="n">
         <v>2019</v>
@@ -4746,16 +4746,16 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>183.26</v>
+        <v>97.23</v>
       </c>
       <c r="D241" t="n">
         <v>2019</v>
@@ -4764,16 +4764,16 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>288.52</v>
+        <v>183.26</v>
       </c>
       <c r="D242" t="n">
         <v>2019</v>
@@ -4782,16 +4782,16 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>385.24</v>
+        <v>288.52</v>
       </c>
       <c r="D243" t="n">
         <v>2019</v>
@@ -4800,16 +4800,16 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>55.43</v>
+        <v>385.24</v>
       </c>
       <c r="D244" t="n">
         <v>2019</v>
@@ -4818,16 +4818,16 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>16.7</v>
+        <v>55.43</v>
       </c>
       <c r="D245" t="n">
         <v>2019</v>
@@ -4836,16 +4836,16 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>57.41</v>
+        <v>16.7</v>
       </c>
       <c r="D246" t="n">
         <v>2019</v>
@@ -4854,16 +4854,16 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>428.51</v>
+        <v>57.41</v>
       </c>
       <c r="D247" t="n">
         <v>2019</v>
@@ -4872,35 +4872,35 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>428.51</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C248" t="n">
+      <c r="C249" t="n">
         <v>488.46</v>
-      </c>
-      <c r="D248" t="n">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>136.82</v>
       </c>
       <c r="D249" t="n">
         <v>2019</v>
@@ -4909,16 +4909,16 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>48.85</v>
+        <v>136.82</v>
       </c>
       <c r="D250" t="n">
         <v>2019</v>
@@ -4927,16 +4927,16 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>13.19</v>
+        <v>48.85</v>
       </c>
       <c r="D251" t="n">
         <v>2019</v>
@@ -4945,16 +4945,16 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>5.43</v>
+        <v>13.19</v>
       </c>
       <c r="D252" t="n">
         <v>2019</v>
@@ -4963,16 +4963,16 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>9.109999999999999</v>
+        <v>5.43</v>
       </c>
       <c r="D253" t="n">
         <v>2019</v>
@@ -4981,16 +4981,16 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3.51</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D254" t="n">
         <v>2019</v>
@@ -4999,16 +4999,16 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>5.49</v>
+        <v>3.51</v>
       </c>
       <c r="D255" t="n">
         <v>2019</v>
@@ -5017,16 +5017,16 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>32.87</v>
+        <v>5.49</v>
       </c>
       <c r="D256" t="n">
         <v>2019</v>
@@ -5035,16 +5035,16 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1260.01</v>
+        <v>32.87</v>
       </c>
       <c r="D257" t="n">
         <v>2019</v>
@@ -5053,16 +5053,16 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>21.9</v>
+        <v>1260.01</v>
       </c>
       <c r="D258" t="n">
         <v>2019</v>
@@ -5071,16 +5071,16 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>19.88</v>
+        <v>21.9</v>
       </c>
       <c r="D259" t="n">
         <v>2019</v>
@@ -5089,16 +5089,16 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>92.44</v>
+        <v>19.88</v>
       </c>
       <c r="D260" t="n">
         <v>2019</v>
@@ -5107,16 +5107,16 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>43.53</v>
+        <v>92.44</v>
       </c>
       <c r="D261" t="n">
         <v>2019</v>
@@ -5125,16 +5125,16 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>99.73</v>
+        <v>43.53</v>
       </c>
       <c r="D262" t="n">
         <v>2019</v>
@@ -5143,16 +5143,16 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>5.92</v>
+        <v>99.73</v>
       </c>
       <c r="D263" t="n">
         <v>2019</v>
@@ -5161,16 +5161,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>102.06</v>
+        <v>5.92</v>
       </c>
       <c r="D264" t="n">
         <v>2019</v>
@@ -5179,16 +5179,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>40.5</v>
+        <v>102.06</v>
       </c>
       <c r="D265" t="n">
         <v>2019</v>
@@ -5197,16 +5197,16 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>280.59</v>
+        <v>40.5</v>
       </c>
       <c r="D266" t="n">
         <v>2019</v>
@@ -5215,16 +5215,16 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>12.34</v>
+        <v>280.59</v>
       </c>
       <c r="D267" t="n">
         <v>2019</v>
@@ -5233,16 +5233,16 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>40.21</v>
+        <v>12.34</v>
       </c>
       <c r="D268" t="n">
         <v>2019</v>
@@ -5251,16 +5251,16 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>67.56999999999999</v>
+        <v>40.21</v>
       </c>
       <c r="D269" t="n">
         <v>2019</v>
@@ -5269,16 +5269,16 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>14.87</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="D270" t="n">
         <v>2019</v>
@@ -5287,16 +5287,16 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>382.75</v>
+        <v>14.87</v>
       </c>
       <c r="D271" t="n">
         <v>2019</v>
@@ -5305,16 +5305,16 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>4.35</v>
+        <v>382.75</v>
       </c>
       <c r="D272" t="n">
         <v>2019</v>
@@ -5323,16 +5323,16 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>528.8</v>
+        <v>4.35</v>
       </c>
       <c r="D273" t="n">
         <v>2019</v>
@@ -5341,16 +5341,16 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>26.52</v>
+        <v>528.8</v>
       </c>
       <c r="D274" t="n">
         <v>2019</v>
@@ -5359,34 +5359,34 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>93.84999999999999</v>
+        <v>26.52</v>
       </c>
       <c r="D275" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>7.15</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="D276" t="n">
         <v>2018</v>
@@ -5395,16 +5395,16 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>257.41</v>
+        <v>7.15</v>
       </c>
       <c r="D277" t="n">
         <v>2018</v>
@@ -5413,16 +5413,16 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>203.57</v>
+        <v>257.41</v>
       </c>
       <c r="D278" t="n">
         <v>2018</v>
@@ -5431,16 +5431,16 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>94.72</v>
+        <v>203.57</v>
       </c>
       <c r="D279" t="n">
         <v>2018</v>
@@ -5449,16 +5449,16 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>169.27</v>
+        <v>94.72</v>
       </c>
       <c r="D280" t="n">
         <v>2018</v>
@@ -5467,16 +5467,16 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>266.01</v>
+        <v>169.27</v>
       </c>
       <c r="D281" t="n">
         <v>2018</v>
@@ -5485,16 +5485,16 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>352.48</v>
+        <v>266.01</v>
       </c>
       <c r="D282" t="n">
         <v>2018</v>
@@ -5503,16 +5503,16 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>52.1</v>
+        <v>352.48</v>
       </c>
       <c r="D283" t="n">
         <v>2018</v>
@@ -5521,16 +5521,16 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>15.86</v>
+        <v>52.1</v>
       </c>
       <c r="D284" t="n">
         <v>2018</v>
@@ -5539,16 +5539,16 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>54.57</v>
+        <v>15.86</v>
       </c>
       <c r="D285" t="n">
         <v>2018</v>
@@ -5557,16 +5557,16 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>406.66</v>
+        <v>54.57</v>
       </c>
       <c r="D286" t="n">
         <v>2018</v>
@@ -5575,35 +5575,35 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>406.66</v>
+      </c>
+      <c r="D287" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C287" t="n">
+      <c r="C288" t="n">
         <v>459.49</v>
-      </c>
-      <c r="D287" t="n">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C288" t="n">
-        <v>136.91</v>
       </c>
       <c r="D288" t="n">
         <v>2018</v>
@@ -5612,16 +5612,16 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>43.98</v>
+        <v>136.91</v>
       </c>
       <c r="D289" t="n">
         <v>2018</v>
@@ -5630,16 +5630,16 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>12.76</v>
+        <v>43.98</v>
       </c>
       <c r="D290" t="n">
         <v>2018</v>
@@ -5648,16 +5648,16 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>5.04</v>
+        <v>12.76</v>
       </c>
       <c r="D291" t="n">
         <v>2018</v>
@@ -5666,16 +5666,16 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>8.449999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="D292" t="n">
         <v>2018</v>
@@ -5684,16 +5684,16 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>3.12</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D293" t="n">
         <v>2018</v>
@@ -5702,16 +5702,16 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>5.02</v>
+        <v>3.12</v>
       </c>
       <c r="D294" t="n">
         <v>2018</v>
@@ -5720,16 +5720,16 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>31.33</v>
+        <v>5.02</v>
       </c>
       <c r="D295" t="n">
         <v>2018</v>
@@ -5738,16 +5738,16 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1141.3</v>
+        <v>31.33</v>
       </c>
       <c r="D296" t="n">
         <v>2018</v>
@@ -5756,16 +5756,16 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>20.59</v>
+        <v>1141.3</v>
       </c>
       <c r="D297" t="n">
         <v>2018</v>
@@ -5774,16 +5774,16 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>17.93</v>
+        <v>20.59</v>
       </c>
       <c r="D298" t="n">
         <v>2018</v>
@@ -5792,16 +5792,16 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>85.43000000000001</v>
+        <v>17.93</v>
       </c>
       <c r="D299" t="n">
         <v>2018</v>
@@ -5810,16 +5810,16 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>42.36</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="D300" t="n">
         <v>2018</v>
@@ -5828,16 +5828,16 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>95.47</v>
+        <v>42.36</v>
       </c>
       <c r="D301" t="n">
         <v>2018</v>
@@ -5846,16 +5846,16 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>5.5</v>
+        <v>95.47</v>
       </c>
       <c r="D302" t="n">
         <v>2018</v>
@@ -5864,16 +5864,16 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>91.91</v>
+        <v>5.5</v>
       </c>
       <c r="D303" t="n">
         <v>2018</v>
@@ -5882,16 +5882,16 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>39.67</v>
+        <v>91.91</v>
       </c>
       <c r="D304" t="n">
         <v>2018</v>
@@ -5900,16 +5900,16 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>255.43</v>
+        <v>39.67</v>
       </c>
       <c r="D305" t="n">
         <v>2018</v>
@@ -5918,16 +5918,16 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>10.66</v>
+        <v>255.43</v>
       </c>
       <c r="D306" t="n">
         <v>2018</v>
@@ -5936,16 +5936,16 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>37.69</v>
+        <v>10.66</v>
       </c>
       <c r="D307" t="n">
         <v>2018</v>
@@ -5954,16 +5954,16 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>72.95999999999999</v>
+        <v>37.69</v>
       </c>
       <c r="D308" t="n">
         <v>2018</v>
@@ -5972,16 +5972,16 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>12.68</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="D309" t="n">
         <v>2018</v>
@@ -5990,16 +5990,16 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>344.71</v>
+        <v>12.68</v>
       </c>
       <c r="D310" t="n">
         <v>2018</v>
@@ -6008,16 +6008,16 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>4.28</v>
+        <v>344.71</v>
       </c>
       <c r="D311" t="n">
         <v>2018</v>
@@ -6026,16 +6026,16 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>487.74</v>
+        <v>4.28</v>
       </c>
       <c r="D312" t="n">
         <v>2018</v>
@@ -6044,16 +6044,16 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>26.11</v>
+        <v>487.74</v>
       </c>
       <c r="D313" t="n">
         <v>2018</v>
@@ -6062,34 +6062,34 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>88.76000000000001</v>
+        <v>26.11</v>
       </c>
       <c r="D314" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>6.78</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="D315" t="n">
         <v>2017</v>
@@ -6098,16 +6098,16 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>249.99</v>
+        <v>6.78</v>
       </c>
       <c r="D316" t="n">
         <v>2017</v>
@@ -6116,16 +6116,16 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>191.07</v>
+        <v>249.99</v>
       </c>
       <c r="D317" t="n">
         <v>2017</v>
@@ -6134,16 +6134,16 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>102.2</v>
+        <v>191.07</v>
       </c>
       <c r="D318" t="n">
         <v>2017</v>
@@ -6152,16 +6152,16 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>168.95</v>
+        <v>102.2</v>
       </c>
       <c r="D319" t="n">
         <v>2017</v>
@@ -6170,16 +6170,16 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>Белорусский рубль</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>251.61</v>
+        <v>168.95</v>
       </c>
       <c r="D320" t="n">
         <v>2017</v>
@@ -6188,16 +6188,16 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>331.19</v>
+        <v>251.61</v>
       </c>
       <c r="D321" t="n">
         <v>2017</v>
@@ -6206,16 +6206,16 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>48.28</v>
+        <v>331.19</v>
       </c>
       <c r="D322" t="n">
         <v>2017</v>
@@ -6224,16 +6224,16 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>14.02</v>
+        <v>48.28</v>
       </c>
       <c r="D323" t="n">
         <v>2017</v>
@@ -6242,16 +6242,16 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>49.52</v>
+        <v>14.02</v>
       </c>
       <c r="D324" t="n">
         <v>2017</v>
@@ -6260,16 +6260,16 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>368.32</v>
+        <v>49.52</v>
       </c>
       <c r="D325" t="n">
         <v>2017</v>
@@ -6277,37 +6277,37 @@
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
+        <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>Фунт стерлингов
 Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C326" t="n">
+      <c r="C327" t="n">
         <v>419.99</v>
-      </c>
-      <c r="D326" t="n">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>130.87</v>
       </c>
       <c r="D327" t="n">
         <v>2017</v>
@@ -6316,16 +6316,16 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>41.84</v>
+        <v>130.87</v>
       </c>
       <c r="D328" t="n">
         <v>2017</v>
@@ -6334,16 +6334,16 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>11.92</v>
+        <v>41.84</v>
       </c>
       <c r="D329" t="n">
         <v>2017</v>
@@ -6352,16 +6352,16 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>5.01</v>
+        <v>11.92</v>
       </c>
       <c r="D330" t="n">
         <v>2017</v>
@@ -6370,16 +6370,16 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>9.82</v>
+        <v>5.01</v>
       </c>
       <c r="D331" t="n">
         <v>2017</v>
@@ -6388,16 +6388,16 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>2.91</v>
+        <v>9.82</v>
       </c>
       <c r="D332" t="n">
         <v>2017</v>
@@ -6406,16 +6406,16 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>4.74</v>
+        <v>2.91</v>
       </c>
       <c r="D333" t="n">
         <v>2017</v>
@@ -6424,35 +6424,35 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
+          <t>Кыргызский сом</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
           <t>100 Вон Республики
 Корея</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="C334" t="n">
+      <c r="C335" t="n">
         <v>28.86</v>
-      </c>
-      <c r="D334" t="n">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Кувейтский динар</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>KWD</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>1075.29</v>
       </c>
       <c r="D335" t="n">
         <v>2017</v>
@@ -6461,16 +6461,16 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>17.78</v>
+        <v>1075.29</v>
       </c>
       <c r="D336" t="n">
         <v>2017</v>
@@ -6479,16 +6479,16 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>17.27</v>
+        <v>17.78</v>
       </c>
       <c r="D337" t="n">
         <v>2017</v>
@@ -6497,16 +6497,16 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>75.92</v>
+        <v>17.27</v>
       </c>
       <c r="D338" t="n">
         <v>2017</v>
@@ -6515,16 +6515,16 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>39.49</v>
+        <v>75.92</v>
       </c>
       <c r="D339" t="n">
         <v>2017</v>
@@ -6533,16 +6533,16 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>86.54000000000001</v>
+        <v>39.49</v>
       </c>
       <c r="D340" t="n">
         <v>2017</v>
@@ -6551,16 +6551,16 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>5.59</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="D341" t="n">
         <v>2017</v>
@@ -6569,16 +6569,16 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>86.93000000000001</v>
+        <v>5.59</v>
       </c>
       <c r="D342" t="n">
         <v>2017</v>
@@ -6587,16 +6587,16 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>38.23</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="D343" t="n">
         <v>2017</v>
@@ -6605,16 +6605,16 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>236.22</v>
+        <v>38.23</v>
       </c>
       <c r="D344" t="n">
         <v>2017</v>
@@ -6623,16 +6623,16 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>9.619999999999999</v>
+        <v>236.22</v>
       </c>
       <c r="D345" t="n">
         <v>2017</v>
@@ -6641,16 +6641,16 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>38.04</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D346" t="n">
         <v>2017</v>
@@ -6659,16 +6659,16 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>89.45</v>
+        <v>38.04</v>
       </c>
       <c r="D347" t="n">
         <v>2017</v>
@@ -6677,16 +6677,16 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>12.27</v>
+        <v>89.45</v>
       </c>
       <c r="D348" t="n">
         <v>2017</v>
@@ -6695,16 +6695,16 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>326</v>
+        <v>12.27</v>
       </c>
       <c r="D349" t="n">
         <v>2017</v>
@@ -6713,16 +6713,16 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>7.28</v>
+        <v>326</v>
       </c>
       <c r="D350" t="n">
         <v>2017</v>
@@ -6731,16 +6731,16 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>452.08</v>
+        <v>7.28</v>
       </c>
       <c r="D351" t="n">
         <v>2017</v>
@@ -6749,16 +6749,16 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>24.49</v>
+        <v>452.08</v>
       </c>
       <c r="D352" t="n">
         <v>2017</v>
@@ -6767,34 +6767,34 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>93.16</v>
+        <v>24.49</v>
       </c>
       <c r="D353" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>10 Армянских драмов</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>7.15</v>
+        <v>93.16</v>
       </c>
       <c r="D354" t="n">
         <v>2016</v>
@@ -6803,16 +6803,16 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Австралийский доллар</t>
+          <t>10 Армянских драмов</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>254.25</v>
+        <v>7.15</v>
       </c>
       <c r="D355" t="n">
         <v>2016</v>
@@ -6821,16 +6821,16 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийский доллар</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>217.41</v>
+        <v>254.25</v>
       </c>
       <c r="D356" t="n">
         <v>2016</v>
@@ -6839,16 +6839,16 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>98.42</v>
+        <v>217.41</v>
       </c>
       <c r="D357" t="n">
         <v>2016</v>
@@ -6857,16 +6857,16 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>100 Белорусских рублей*</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>BYN</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>87.63</v>
+        <v>98.42</v>
       </c>
       <c r="D358" t="n">
         <v>2016</v>
@@ -6875,16 +6875,16 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>100 Белорусских рублей*</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYN</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>258.06</v>
+        <v>87.63</v>
       </c>
       <c r="D359" t="n">
         <v>2016</v>
@@ -6893,16 +6893,16 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>347.37</v>
+        <v>258.06</v>
       </c>
       <c r="D360" t="n">
         <v>2016</v>
@@ -6911,16 +6911,16 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>51.55</v>
+        <v>347.37</v>
       </c>
       <c r="D361" t="n">
         <v>2016</v>
@@ -6929,16 +6929,16 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>14.01</v>
+        <v>51.55</v>
       </c>
       <c r="D362" t="n">
         <v>2016</v>
@@ -6947,16 +6947,16 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>50.86</v>
+        <v>14.01</v>
       </c>
       <c r="D363" t="n">
         <v>2016</v>
@@ -6965,16 +6965,16 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>378.63</v>
+        <v>50.86</v>
       </c>
       <c r="D364" t="n">
         <v>2016</v>
@@ -6983,35 +6983,35 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
           <t>Фунт стерлингов Соединенного
 Королевства</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C365" t="n">
+      <c r="C366" t="n">
         <v>464.39</v>
-      </c>
-      <c r="D365" t="n">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>146.12</v>
       </c>
       <c r="D366" t="n">
         <v>2016</v>
@@ -7020,16 +7020,16 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>44.08</v>
+        <v>146.12</v>
       </c>
       <c r="D367" t="n">
         <v>2016</v>
@@ -7038,16 +7038,16 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>10 Венгерских форинтов</t>
+          <t>Гонконгский доллар</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>12.16</v>
+        <v>44.08</v>
       </c>
       <c r="D368" t="n">
         <v>2016</v>
@@ -7056,16 +7056,16 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерских форинтов</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>5.09</v>
+        <v>12.16</v>
       </c>
       <c r="D369" t="n">
         <v>2016</v>
@@ -7074,16 +7074,16 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1000 Иранских риалов</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>11.24</v>
+        <v>5.09</v>
       </c>
       <c r="D370" t="n">
         <v>2016</v>
@@ -7092,16 +7092,16 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Японская йена</t>
+          <t>1000 Иранских риалов</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3.15</v>
+        <v>11.24</v>
       </c>
       <c r="D371" t="n">
         <v>2016</v>
@@ -7110,16 +7110,16 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Кыргызский сом</t>
+          <t>Японская йена</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>4.89</v>
+        <v>3.15</v>
       </c>
       <c r="D372" t="n">
         <v>2016</v>
@@ -7128,16 +7128,16 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>100 Вон Республики Корея</t>
+          <t>Кыргызский сом</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>29.5</v>
+        <v>4.89</v>
       </c>
       <c r="D373" t="n">
         <v>2016</v>
@@ -7146,16 +7146,16 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Вон Республики Корея</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1132.52</v>
+        <v>29.5</v>
       </c>
       <c r="D374" t="n">
         <v>2016</v>
@@ -7164,16 +7164,16 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>17.25</v>
+        <v>1132.52</v>
       </c>
       <c r="D375" t="n">
         <v>2016</v>
@@ -7182,16 +7182,16 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>18.37</v>
+        <v>17.25</v>
       </c>
       <c r="D376" t="n">
         <v>2016</v>
@@ -7200,16 +7200,16 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>82.72</v>
+        <v>18.37</v>
       </c>
       <c r="D377" t="n">
         <v>2016</v>
@@ -7218,16 +7218,16 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>40.74</v>
+        <v>82.72</v>
       </c>
       <c r="D378" t="n">
         <v>2016</v>
@@ -7236,16 +7236,16 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>86.81999999999999</v>
+        <v>40.74</v>
       </c>
       <c r="D379" t="n">
         <v>2016</v>
@@ -7254,16 +7254,16 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>5.11</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="D380" t="n">
         <v>2016</v>
@@ -7272,16 +7272,16 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>91.23999999999999</v>
+        <v>5.11</v>
       </c>
       <c r="D381" t="n">
         <v>2016</v>
@@ -7290,16 +7290,16 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>40.06</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="D382" t="n">
         <v>2016</v>
@@ -7308,16 +7308,16 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>247.86</v>
+        <v>40.06</v>
       </c>
       <c r="D383" t="n">
         <v>2016</v>
@@ -7326,16 +7326,16 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>9.699999999999999</v>
+        <v>247.86</v>
       </c>
       <c r="D384" t="n">
         <v>2016</v>
@@ -7344,16 +7344,16 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>43.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D385" t="n">
         <v>2016</v>
@@ -7362,16 +7362,16 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>113.65</v>
+        <v>43.85</v>
       </c>
       <c r="D386" t="n">
         <v>2016</v>
@@ -7380,16 +7380,16 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>Турецкая лира</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>13.42</v>
+        <v>113.65</v>
       </c>
       <c r="D387" t="n">
         <v>2016</v>
@@ -7398,16 +7398,16 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>342.16</v>
+        <v>13.42</v>
       </c>
       <c r="D388" t="n">
         <v>2016</v>
@@ -7416,16 +7416,16 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>100 Узбекских сумов</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>11.61</v>
+        <v>342.16</v>
       </c>
       <c r="D389" t="n">
         <v>2016</v>
@@ -7434,16 +7434,16 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекских сумов</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>475.67</v>
+        <v>11.61</v>
       </c>
       <c r="D390" t="n">
         <v>2016</v>
@@ -7452,16 +7452,16 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Южноафриканский рэнд</t>
+          <t>СДР</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ZAR</t>
+          <t>XDR</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>23.3</v>
+        <v>475.67</v>
       </c>
       <c r="D391" t="n">
         <v>2016</v>
@@ -7470,34 +7470,34 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Дихрам ОАЭ</t>
+          <t>Южноафриканский рэнд</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>60.37</v>
+        <v>23.3</v>
       </c>
       <c r="D392" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>10 Армянский драм</t>
+          <t>Дихрам ОАЭ</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AED</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4.66</v>
+        <v>60.37</v>
       </c>
       <c r="D393" t="n">
         <v>2015</v>
@@ -7506,16 +7506,16 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Австралийск. доллар</t>
+          <t>10 Армянский драм</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>AUD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>165.66</v>
+        <v>4.66</v>
       </c>
       <c r="D394" t="n">
         <v>2015</v>
@@ -7524,16 +7524,16 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Азербайджанский манат</t>
+          <t>Австралийск. доллар</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>217.23</v>
+        <v>165.66</v>
       </c>
       <c r="D395" t="n">
         <v>2015</v>
@@ -7542,16 +7542,16 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Бразильский реал</t>
+          <t>Азербайджанский манат</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>66.27</v>
+        <v>217.23</v>
       </c>
       <c r="D396" t="n">
         <v>2015</v>
@@ -7560,16 +7560,16 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>100 Белорусский рубль</t>
+          <t>Бразильский реал</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>BYR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1.38</v>
+        <v>66.27</v>
       </c>
       <c r="D397" t="n">
         <v>2015</v>
@@ -7578,16 +7578,16 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Канадский доллар</t>
+          <t>100 Белорусский рубль</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>BYR</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>172.57</v>
+        <v>1.38</v>
       </c>
       <c r="D398" t="n">
         <v>2015</v>
@@ -7596,16 +7596,16 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Швейцарский франк</t>
+          <t>Канадский доллар</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>229.76</v>
+        <v>172.57</v>
       </c>
       <c r="D399" t="n">
         <v>2015</v>
@@ -7614,16 +7614,16 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Китайский юань</t>
+          <t>Швейцарский франк</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>35.2</v>
+        <v>229.76</v>
       </c>
       <c r="D400" t="n">
         <v>2015</v>
@@ -7632,16 +7632,16 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Чешская крона</t>
+          <t>Китайский юань</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>CZK</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>9.029999999999999</v>
+        <v>35.2</v>
       </c>
       <c r="D401" t="n">
         <v>2015</v>
@@ -7650,16 +7650,16 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Датская крона</t>
+          <t>Чешская крона</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>DKK</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>32.96</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D402" t="n">
         <v>2015</v>
@@ -7668,16 +7668,16 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Евро</t>
+          <t>Датская крона</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>245.8</v>
+        <v>32.96</v>
       </c>
       <c r="D403" t="n">
         <v>2015</v>
@@ -7686,35 +7686,35 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>Евро</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="D404" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
           <t>Английский фунт
 стерлингов</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="C404" t="n">
+      <c r="C405" t="n">
         <v>338.76</v>
-      </c>
-      <c r="D404" t="n">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Грузинский лари</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>GEL</t>
-        </is>
-      </c>
-      <c r="C405" t="n">
-        <v>98.06999999999999</v>
       </c>
       <c r="D405" t="n">
         <v>2015</v>
@@ -7723,16 +7723,16 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1 Гонконгский доллар</t>
+          <t>Грузинский лари</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>GEL</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>28.6</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="D406" t="n">
         <v>2015</v>
@@ -7741,16 +7741,16 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>10 Венгерский форинт</t>
+          <t>1 Гонконгский доллар</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>HUF</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>7.93</v>
+        <v>28.6</v>
       </c>
       <c r="D407" t="n">
         <v>2015</v>
@@ -7759,16 +7759,16 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Индийская рупия</t>
+          <t>10 Венгерский форинт</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>HUF</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>3.44</v>
+        <v>7.93</v>
       </c>
       <c r="D408" t="n">
         <v>2015</v>
@@ -7777,16 +7777,16 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1000 Иранский риал</t>
+          <t>Индийская рупия</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>IRR</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>7.62</v>
+        <v>3.44</v>
       </c>
       <c r="D409" t="n">
         <v>2015</v>
@@ -7795,16 +7795,16 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1 японская йена</t>
+          <t>1000 Иранский риал</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>IRR</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1.83</v>
+        <v>7.62</v>
       </c>
       <c r="D410" t="n">
         <v>2015</v>
@@ -7813,16 +7813,16 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Киргизский сом</t>
+          <t>1 японская йена</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>KGS</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>3.43</v>
+        <v>1.83</v>
       </c>
       <c r="D411" t="n">
         <v>2015</v>
@@ -7831,16 +7831,16 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>100 Южно-корейских вон</t>
+          <t>Киргизский сом</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>KGS</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>19.54</v>
+        <v>3.43</v>
       </c>
       <c r="D412" t="n">
         <v>2015</v>
@@ -7849,16 +7849,16 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Кувейтский динар</t>
+          <t>100 Южно-корейских вон</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>KWD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>736.27</v>
+        <v>19.54</v>
       </c>
       <c r="D413" t="n">
         <v>2015</v>
@@ -7867,16 +7867,16 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Молдавский лей</t>
+          <t>Кувейтский динар</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>KWD</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>11.82</v>
+        <v>736.27</v>
       </c>
       <c r="D414" t="n">
         <v>2015</v>
@@ -7885,16 +7885,16 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Мексиканский песо</t>
+          <t>Молдавский лей</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>13.89</v>
+        <v>11.82</v>
       </c>
       <c r="D415" t="n">
         <v>2015</v>
@@ -7903,16 +7903,16 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Малазийский ринггит</t>
+          <t>Мексиканский песо</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>MYR</t>
+          <t>MXN</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>56.31</v>
+        <v>13.89</v>
       </c>
       <c r="D416" t="n">
         <v>2015</v>
@@ -7921,16 +7921,16 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Норвежская крона</t>
+          <t>Малазийский ринггит</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>NOK</t>
+          <t>MYR</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>27.35</v>
+        <v>56.31</v>
       </c>
       <c r="D417" t="n">
         <v>2015</v>
@@ -7939,16 +7939,16 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Польский злотый</t>
+          <t>Норвежская крона</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>NOK</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>58.63</v>
+        <v>27.35</v>
       </c>
       <c r="D418" t="n">
         <v>2015</v>
@@ -7957,16 +7957,16 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Российский рубль</t>
+          <t>Польский злотый</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>RUB</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3.61</v>
+        <v>58.63</v>
       </c>
       <c r="D419" t="n">
         <v>2015</v>
@@ -7975,16 +7975,16 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Риял Саудовской Аравии</t>
+          <t>Российский рубль</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SAR</t>
+          <t>RUB</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>59.12</v>
+        <v>3.61</v>
       </c>
       <c r="D420" t="n">
         <v>2015</v>
@@ -7993,16 +7993,16 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Шведская крона</t>
+          <t>Риял Саудовской Аравии</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>SAR</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>26.3</v>
+        <v>59.12</v>
       </c>
       <c r="D421" t="n">
         <v>2015</v>
@@ -8011,16 +8011,16 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Сингапурский доллар</t>
+          <t>Шведская крона</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>160.79</v>
+        <v>26.3</v>
       </c>
       <c r="D422" t="n">
         <v>2015</v>
@@ -8029,16 +8029,16 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Тайский бат</t>
+          <t>Сингапурский доллар</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>THВ</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>6.44</v>
+        <v>160.79</v>
       </c>
       <c r="D423" t="n">
         <v>2015</v>
@@ -8047,16 +8047,16 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Таджикский сомони</t>
+          <t>Тайский бат</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>TJS</t>
+          <t>THВ</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>36.06</v>
+        <v>6.44</v>
       </c>
       <c r="D424" t="n">
         <v>2015</v>
@@ -8065,16 +8065,16 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1 турецкая лира</t>
+          <t>Таджикский сомони</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>TJS</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>80.98</v>
+        <v>36.06</v>
       </c>
       <c r="D425" t="n">
         <v>2015</v>
@@ -8083,16 +8083,16 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Украинская гривна</t>
+          <t>1 турецкая лира</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>UAH</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>10.27</v>
+        <v>80.98</v>
       </c>
       <c r="D426" t="n">
         <v>2015</v>
@@ -8101,16 +8101,16 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Доллар США</t>
+          <t>Украинская гривна</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>UAH</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>221.73</v>
+        <v>10.27</v>
       </c>
       <c r="D427" t="n">
         <v>2015</v>
@@ -8119,16 +8119,16 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>100 Узбекский сум</t>
+          <t>Доллар США</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>UZS</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>8.609999999999999</v>
+        <v>221.73</v>
       </c>
       <c r="D428" t="n">
         <v>2015</v>
@@ -8137,16 +8137,16 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>СДР</t>
+          <t>100 Узбекский сум</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>XDR</t>
+          <t>UZS</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>310.12</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D429" t="n">
         <v>2015</v>
@@ -8155,18 +8155,36 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
+          <t>СДР</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>XDR</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>310.12</v>
+      </c>
+      <c r="D430" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
           <t>Южно-африканский рэнд</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>ZAR</t>
         </is>
       </c>
-      <c r="C430" t="n">
+      <c r="C431" t="n">
         <v>17.23</v>
       </c>
-      <c r="D430" t="n">
+      <c r="D431" t="n">
         <v>2015</v>
       </c>
     </row>
